--- a/data/trans_camb/IP16B01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,92; 94,01</t>
+          <t>52,23; 94,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 72,69</t>
+          <t>10,87; 73,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,89; 100,0</t>
+          <t>70,9; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,47; 93,78</t>
+          <t>48,41; 92,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,26; 95,28</t>
+          <t>69,23; 94,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,8; 81,3</t>
+          <t>41,97; 80,31</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,68; 95,59</t>
+          <t>63,09; 95,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,45; 96,79</t>
+          <t>71,43; 96,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>73,65; 100,0</t>
+          <t>74,89; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,49; 93,76</t>
+          <t>75,67; 94,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,73; 97,91</t>
+          <t>79,93; 97,84</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,36; 100,0</t>
+          <t>83,28; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,42; 100,0</t>
+          <t>87,52; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,35; 100,0</t>
+          <t>62,66; 100,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,33; 91,52</t>
+          <t>53,94; 91,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65,54; 100,0</t>
+          <t>63,76; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>67,36; 100,0</t>
+          <t>66,62; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61,03; 95,05</t>
+          <t>60,33; 95,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,78; 92,09</t>
+          <t>67,39; 94,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,63; 94,87</t>
+          <t>73,51; 94,6</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57,53; 94,68</t>
+          <t>58,94; 94,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54,34; 100,0</t>
+          <t>46,38; 100,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64,12; 93,2</t>
+          <t>63,58; 93,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>30,53; 92,28</t>
+          <t>31,09; 92,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25,49; 88,21</t>
+          <t>19,67; 87,7</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63,71; 100,0</t>
+          <t>70,43; 100,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19,63; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>63,53; 95,63</t>
+          <t>62,38; 95,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,72; 90,61</t>
+          <t>28,01; 91,05</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>64,72; 95,79</t>
+          <t>64,76; 95,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>38,8; 86,69</t>
+          <t>37,55; 86,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100,0</t>
+          <t>76,72; 100,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>75,65; 95,67</t>
+          <t>77,75; 95,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,52; 92,53</t>
+          <t>62,12; 92,8</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>45,0; 93,92</t>
+          <t>46,41; 91,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>65,36; 100,0</t>
+          <t>59,32; 100,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1738,17 +1738,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>66,69; 100,0</t>
+          <t>74,05; 100,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>71,32; 97,03</t>
+          <t>70,62; 96,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>76,46; 98,07</t>
+          <t>74,24; 99,01</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>74,24; 86,95</t>
+          <t>74,06; 87,17</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>72,36; 87,82</t>
+          <t>72,17; 87,06</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>83,27; 90,84</t>
+          <t>83,07; 90,83</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>79,33; 89,01</t>
+          <t>78,98; 88,59</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2147,22; —</t>
+          <t>2177,73; —</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2188,07; —</t>
+          <t>2006,35; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5034,97; —</t>
+          <t>5681,2; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4693,67; —</t>
+          <t>5285,63; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B01-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B01-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,23; 94,46</t>
+          <t>52,44; 94,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,87; 73,81</t>
+          <t>12,84; 76,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,9; 100,0</t>
+          <t>69,61; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,41; 92,68</t>
+          <t>49,22; 93,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,23; 94,72</t>
+          <t>69,87; 94,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,97; 80,31</t>
+          <t>40,46; 79,83</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,09; 95,5</t>
+          <t>59,52; 95,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,43; 96,72</t>
+          <t>70,33; 96,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,89; 100,0</t>
+          <t>71,07; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75,67; 94,17</t>
+          <t>75,43; 95,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,93; 97,84</t>
+          <t>81,11; 97,83</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,28; 100,0</t>
+          <t>79,72; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,99; 100,0</t>
+          <t>40,23; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,52; 100,0</t>
+          <t>89,12; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,66; 100,0</t>
+          <t>65,35; 100,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,94; 91,54</t>
+          <t>54,1; 91,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,76; 100,0</t>
+          <t>66,5; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66,62; 100,0</t>
+          <t>66,63; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,33; 95,71</t>
+          <t>62,57; 95,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,39; 94,14</t>
+          <t>66,29; 93,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,51; 94,6</t>
+          <t>72,09; 93,32</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>58,94; 94,44</t>
+          <t>56,92; 94,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46,38; 100,0</t>
+          <t>46,31; 100,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>63,58; 93,01</t>
+          <t>64,19; 93,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>31,09; 92,43</t>
+          <t>31,16; 92,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>19,67; 87,7</t>
+          <t>19,4; 87,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70,43; 100,0</t>
+          <t>69,55; 100,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>19,63; 100,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>62,38; 95,59</t>
+          <t>64,0; 95,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,01; 91,05</t>
+          <t>28,46; 90,89</t>
         </is>
       </c>
     </row>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>64,76; 95,77</t>
+          <t>62,16; 95,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>37,55; 86,36</t>
+          <t>40,62; 86,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76,72; 100,0</t>
+          <t>76,21; 100,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>77,75; 95,63</t>
+          <t>75,56; 95,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,12; 92,8</t>
+          <t>62,49; 93,05</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>46,41; 91,81</t>
+          <t>46,12; 93,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>59,32; 100,0</t>
+          <t>62,18; 100,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1738,17 +1738,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>74,05; 100,0</t>
+          <t>66,94; 100,0</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>70,62; 96,77</t>
+          <t>70,63; 96,77</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>74,24; 99,01</t>
+          <t>76,83; 98,54</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>74,06; 87,17</t>
+          <t>73,61; 87,07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>72,17; 87,06</t>
+          <t>72,02; 86,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>83,07; 90,83</t>
+          <t>83,1; 90,82</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>78,98; 88,59</t>
+          <t>78,97; 88,82</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2177,73; —</t>
+          <t>2357,06; —</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2006,35; —</t>
+          <t>2324,28; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>5681,2; —</t>
+          <t>4396,5; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5285,63; —</t>
+          <t>4694,45; —</t>
         </is>
       </c>
     </row>
